--- a/docs/工程進度甘特圖.xlsx
+++ b/docs/工程進度甘特圖.xlsx
@@ -11,6 +11,7 @@
     <sheet name="工程進度表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="預算總覽" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="工程安排建議" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="分區進場時程" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'工程進度表'!$A$1:$I$35</definedName>
@@ -26,7 +27,7 @@
     <numFmt numFmtId="165" formatCode="m/d"/>
     <numFmt numFmtId="166" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -103,8 +104,16 @@
       <color rgb="001F3864"/>
       <sz val="12"/>
     </font>
+    <font>
+      <color rgb="00222222"/>
+      <sz val="7"/>
+    </font>
+    <font>
+      <color rgb="00FFFFFF"/>
+      <sz val="7"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="24">
     <fill>
       <patternFill/>
     </fill>
@@ -201,6 +210,26 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="006FA8DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8B500"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C2787F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00BFA35A"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -236,7 +265,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -411,6 +440,25 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -4131,4 +4179,1909 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AI45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="3.4" customWidth="1" min="8" max="8"/>
+    <col width="3.4" customWidth="1" min="9" max="9"/>
+    <col width="3.4" customWidth="1" min="10" max="10"/>
+    <col width="3.4" customWidth="1" min="11" max="11"/>
+    <col width="3.4" customWidth="1" min="12" max="12"/>
+    <col width="3.4" customWidth="1" min="13" max="13"/>
+    <col width="3.4" customWidth="1" min="14" max="14"/>
+    <col width="3.4" customWidth="1" min="15" max="15"/>
+    <col width="3.4" customWidth="1" min="16" max="16"/>
+    <col width="3.4" customWidth="1" min="17" max="17"/>
+    <col width="3.4" customWidth="1" min="18" max="18"/>
+    <col width="3.4" customWidth="1" min="19" max="19"/>
+    <col width="3.4" customWidth="1" min="20" max="20"/>
+    <col width="3.4" customWidth="1" min="21" max="21"/>
+    <col width="3.4" customWidth="1" min="22" max="22"/>
+    <col width="3.4" customWidth="1" min="23" max="23"/>
+    <col width="3.4" customWidth="1" min="24" max="24"/>
+    <col width="3.4" customWidth="1" min="25" max="25"/>
+    <col width="3.4" customWidth="1" min="26" max="26"/>
+    <col width="3.4" customWidth="1" min="27" max="27"/>
+    <col width="3.4" customWidth="1" min="28" max="28"/>
+    <col width="3.4" customWidth="1" min="29" max="29"/>
+    <col width="3.4" customWidth="1" min="30" max="30"/>
+    <col width="3.4" customWidth="1" min="31" max="31"/>
+    <col width="3.4" customWidth="1" min="32" max="32"/>
+    <col width="3.4" customWidth="1" min="33" max="33"/>
+    <col width="3.4" customWidth="1" min="34" max="34"/>
+    <col width="3.4" customWidth="1" min="35" max="35"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="85" t="inlineStr">
+        <is>
+          <t>碧侯教會 室內裝修工程 — 分區進場時程（各區工序對應實際日期）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>色塊＝該區當期工種；依進場順位排列。開工(進場保護) 2026/06/19。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>順位</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>樓層</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>區域</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>進場</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>退場</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>週</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>2026/6月</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>2026/7月</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>2026/8月</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>2026/9月</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>2026/10月</t>
+        </is>
+      </c>
+      <c r="AD4" s="4" t="inlineStr">
+        <is>
+          <t>2026/11月</t>
+        </is>
+      </c>
+      <c r="AI4" s="4" t="inlineStr">
+        <is>
+          <t>2026/12月</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>6/1</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>6/8</t>
+        </is>
+      </c>
+      <c r="J5" s="6" t="inlineStr">
+        <is>
+          <t>6/15</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>6/22</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>6/29</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>7/6</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>7/13</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>7/20</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>7/27</t>
+        </is>
+      </c>
+      <c r="Q5" s="5" t="inlineStr">
+        <is>
+          <t>8/3</t>
+        </is>
+      </c>
+      <c r="R5" s="5" t="inlineStr">
+        <is>
+          <t>8/10</t>
+        </is>
+      </c>
+      <c r="S5" s="5" t="inlineStr">
+        <is>
+          <t>8/17</t>
+        </is>
+      </c>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>8/24</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>8/31</t>
+        </is>
+      </c>
+      <c r="V5" s="5" t="inlineStr">
+        <is>
+          <t>9/7</t>
+        </is>
+      </c>
+      <c r="W5" s="5" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+      <c r="X5" s="5" t="inlineStr">
+        <is>
+          <t>9/21</t>
+        </is>
+      </c>
+      <c r="Y5" s="5" t="inlineStr">
+        <is>
+          <t>9/28</t>
+        </is>
+      </c>
+      <c r="Z5" s="5" t="inlineStr">
+        <is>
+          <t>10/5</t>
+        </is>
+      </c>
+      <c r="AA5" s="5" t="inlineStr">
+        <is>
+          <t>10/12</t>
+        </is>
+      </c>
+      <c r="AB5" s="5" t="inlineStr">
+        <is>
+          <t>10/19</t>
+        </is>
+      </c>
+      <c r="AC5" s="5" t="inlineStr">
+        <is>
+          <t>10/26</t>
+        </is>
+      </c>
+      <c r="AD5" s="5" t="inlineStr">
+        <is>
+          <t>11/2</t>
+        </is>
+      </c>
+      <c r="AE5" s="5" t="inlineStr">
+        <is>
+          <t>11/9</t>
+        </is>
+      </c>
+      <c r="AF5" s="5" t="inlineStr">
+        <is>
+          <t>11/16</t>
+        </is>
+      </c>
+      <c r="AG5" s="5" t="inlineStr">
+        <is>
+          <t>11/23</t>
+        </is>
+      </c>
+      <c r="AH5" s="5" t="inlineStr">
+        <is>
+          <t>11/30</t>
+        </is>
+      </c>
+      <c r="AI5" s="5" t="inlineStr">
+        <is>
+          <t>12/7</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="C6" s="47" t="inlineStr">
+        <is>
+          <t>主會堂(2-3F挑空/夾層/講台) ★</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>46202</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G6" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L6" s="88" t="inlineStr">
+        <is>
+          <t>鷹架</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="O6" s="50" t="n"/>
+      <c r="P6" s="50" t="n"/>
+      <c r="Q6" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="R6" s="26" t="n"/>
+      <c r="S6" s="26" t="n"/>
+      <c r="T6" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="U6" s="30" t="n"/>
+      <c r="V6" s="30" t="n"/>
+      <c r="W6" s="30" t="n"/>
+      <c r="X6" s="92" t="inlineStr">
+        <is>
+          <t>石材</t>
+        </is>
+      </c>
+      <c r="Y6" s="32" t="n"/>
+      <c r="Z6" s="32" t="n"/>
+      <c r="AA6" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB6" s="94" t="inlineStr">
+        <is>
+          <t>金屬</t>
+        </is>
+      </c>
+      <c r="AC6" s="95" t="inlineStr">
+        <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="AD6" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE6" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>全區</t>
+        </is>
+      </c>
+      <c r="C7" s="80" t="inlineStr">
+        <is>
+          <t>甲/乙梯間 + 通廊</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>T10</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>46202</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>46351</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="L7" s="88" t="inlineStr">
+        <is>
+          <t>鷹架</t>
+        </is>
+      </c>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="O7" s="50" t="n"/>
+      <c r="P7" s="50" t="n"/>
+      <c r="Q7" s="50" t="n"/>
+      <c r="R7" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="S7" s="26" t="n"/>
+      <c r="T7" s="26" t="n"/>
+      <c r="U7" s="26" t="n"/>
+      <c r="V7" s="26" t="n"/>
+      <c r="W7" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="X7" s="30" t="n"/>
+      <c r="Y7" s="30" t="n"/>
+      <c r="Z7" s="30" t="n"/>
+      <c r="AA7" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB7" s="51" t="n"/>
+      <c r="AC7" s="51" t="n"/>
+      <c r="AD7" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE7" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+      <c r="AF7" s="98" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="C8" s="80" t="inlineStr">
+        <is>
+          <t>餐廳 / 廚房 / 泡茶區二</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>T7</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M8" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="N8" s="50" t="n"/>
+      <c r="O8" s="50" t="n"/>
+      <c r="P8" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="Q8" s="26" t="n"/>
+      <c r="R8" s="26" t="n"/>
+      <c r="S8" s="26" t="n"/>
+      <c r="T8" s="26" t="n"/>
+      <c r="U8" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="V8" s="30" t="n"/>
+      <c r="W8" s="30" t="n"/>
+      <c r="X8" s="30" t="n"/>
+      <c r="Y8" s="30" t="n"/>
+      <c r="Z8" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AA8" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AB8" s="52" t="n"/>
+      <c r="AC8" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AD8" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE8" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+      <c r="AF8" s="98" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="C9" s="80" t="inlineStr">
+        <is>
+          <t>辦公室/聖器室/影印室/詩班準備</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G9" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M9" s="101" t="inlineStr">
+        <is>
+          <t>拆除</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="18" t="n"/>
+      <c r="P9" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="Q9" s="26" t="n"/>
+      <c r="R9" s="26" t="n"/>
+      <c r="S9" s="26" t="n"/>
+      <c r="T9" s="26" t="n"/>
+      <c r="U9" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="V9" s="30" t="n"/>
+      <c r="W9" s="30" t="n"/>
+      <c r="X9" s="30" t="n"/>
+      <c r="Y9" s="30" t="n"/>
+      <c r="Z9" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AA9" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AB9" s="52" t="n"/>
+      <c r="AC9" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+      <c r="AD9" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE9" s="102" t="n"/>
+      <c r="AF9" s="102" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="10" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="C10" s="80" t="inlineStr">
+        <is>
+          <t>男/女/無障礙廁所</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M10" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="N10" s="103" t="inlineStr">
+        <is>
+          <t>泥作</t>
+        </is>
+      </c>
+      <c r="O10" s="49" t="n"/>
+      <c r="P10" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="Q10" s="26" t="n"/>
+      <c r="R10" s="26" t="n"/>
+      <c r="S10" s="26" t="n"/>
+      <c r="T10" s="104" t="inlineStr">
+        <is>
+          <t>磁磚</t>
+        </is>
+      </c>
+      <c r="U10" s="35" t="n"/>
+      <c r="V10" s="35" t="n"/>
+      <c r="W10" s="35" t="n"/>
+      <c r="X10" s="35" t="n"/>
+      <c r="Y10" s="35" t="n"/>
+      <c r="Z10" s="35" t="n"/>
+      <c r="AA10" s="35" t="n"/>
+      <c r="AB10" s="35" t="n"/>
+      <c r="AC10" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AD10" s="41" t="n"/>
+      <c r="AE10" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+      <c r="AF10" s="98" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>頂樓</t>
+        </is>
+      </c>
+      <c r="C11" s="80" t="inlineStr">
+        <is>
+          <t>頂樓加蓋 / 設備空間</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>T9</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>46209</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>46251</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="M11" s="94" t="inlineStr">
+        <is>
+          <t>金屬</t>
+        </is>
+      </c>
+      <c r="N11" s="20" t="n"/>
+      <c r="O11" s="20" t="n"/>
+      <c r="P11" s="20" t="n"/>
+      <c r="Q11" s="95" t="inlineStr">
+        <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="R11" s="103" t="inlineStr">
+        <is>
+          <t>泥作</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="C12" s="80" t="inlineStr">
+        <is>
+          <t>接待大廳 / 泡茶區一</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>46211</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M12" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="N12" s="50" t="n"/>
+      <c r="O12" s="50" t="n"/>
+      <c r="P12" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="Q12" s="26" t="n"/>
+      <c r="R12" s="26" t="n"/>
+      <c r="S12" s="26" t="n"/>
+      <c r="T12" s="26" t="n"/>
+      <c r="U12" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="V12" s="92" t="inlineStr">
+        <is>
+          <t>石材</t>
+        </is>
+      </c>
+      <c r="W12" s="32" t="n"/>
+      <c r="X12" s="32" t="n"/>
+      <c r="Y12" s="104" t="inlineStr">
+        <is>
+          <t>磁磚</t>
+        </is>
+      </c>
+      <c r="Z12" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AA12" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AB12" s="52" t="n"/>
+      <c r="AC12" s="95" t="inlineStr">
+        <is>
+          <t>玻璃</t>
+        </is>
+      </c>
+      <c r="AD12" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE12" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+      <c r="AF12" s="98" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="C13" s="80" t="inlineStr">
+        <is>
+          <t>幼兒班</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>46211</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M13" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="N13" s="50" t="n"/>
+      <c r="O13" s="50" t="n"/>
+      <c r="P13" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="Q13" s="26" t="n"/>
+      <c r="R13" s="26" t="n"/>
+      <c r="S13" s="26" t="n"/>
+      <c r="T13" s="26" t="n"/>
+      <c r="U13" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="V13" s="30" t="n"/>
+      <c r="W13" s="30" t="n"/>
+      <c r="X13" s="30" t="n"/>
+      <c r="Y13" s="30" t="n"/>
+      <c r="Z13" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AA13" s="51" t="n"/>
+      <c r="AB13" s="51" t="n"/>
+      <c r="AC13" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AD13" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE13" s="102" t="n"/>
+      <c r="AF13" s="102" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>1F</t>
+        </is>
+      </c>
+      <c r="C14" s="80" t="inlineStr">
+        <is>
+          <t>男寢 / 架高通鋪客房</t>
+        </is>
+      </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>46211</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <v>46350</v>
+      </c>
+      <c r="G14" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="M14" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="N14" s="50" t="n"/>
+      <c r="O14" s="50" t="n"/>
+      <c r="P14" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="Q14" s="26" t="n"/>
+      <c r="R14" s="26" t="n"/>
+      <c r="S14" s="26" t="n"/>
+      <c r="T14" s="26" t="n"/>
+      <c r="U14" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="V14" s="30" t="n"/>
+      <c r="W14" s="30" t="n"/>
+      <c r="X14" s="30" t="n"/>
+      <c r="Y14" s="30" t="n"/>
+      <c r="Z14" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AA14" s="51" t="n"/>
+      <c r="AB14" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AC14" s="94" t="inlineStr">
+        <is>
+          <t>金屬</t>
+        </is>
+      </c>
+      <c r="AD14" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE14" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+      <c r="AF14" s="98" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="C15" s="80" t="inlineStr">
+        <is>
+          <t>男/女/無障礙廁所 + 儲藏</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G15" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="N15" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="O15" s="103" t="inlineStr">
+        <is>
+          <t>泥作</t>
+        </is>
+      </c>
+      <c r="P15" s="49" t="n"/>
+      <c r="Q15" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="R15" s="26" t="n"/>
+      <c r="S15" s="26" t="n"/>
+      <c r="T15" s="26" t="n"/>
+      <c r="U15" s="26" t="n"/>
+      <c r="V15" s="26" t="n"/>
+      <c r="W15" s="26" t="n"/>
+      <c r="X15" s="26" t="n"/>
+      <c r="Y15" s="26" t="n"/>
+      <c r="Z15" s="26" t="n"/>
+      <c r="AA15" s="26" t="n"/>
+      <c r="AB15" s="26" t="n"/>
+      <c r="AC15" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AD15" s="41" t="n"/>
+      <c r="AE15" s="41" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="10" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="10" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="C16" s="80" t="inlineStr">
+        <is>
+          <t>接待大廳</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>46218</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="O16" s="50" t="n"/>
+      <c r="P16" s="50" t="n"/>
+      <c r="Q16" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="R16" s="26" t="n"/>
+      <c r="S16" s="26" t="n"/>
+      <c r="T16" s="26" t="n"/>
+      <c r="U16" s="26" t="n"/>
+      <c r="V16" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="W16" s="30" t="n"/>
+      <c r="X16" s="92" t="inlineStr">
+        <is>
+          <t>石材</t>
+        </is>
+      </c>
+      <c r="Y16" s="32" t="n"/>
+      <c r="Z16" s="32" t="n"/>
+      <c r="AA16" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB16" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AC16" s="52" t="n"/>
+      <c r="AD16" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE16" s="102" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="10" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="C17" s="80" t="inlineStr">
+        <is>
+          <t>幼年/國中/少年/高中班</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>46218</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N17" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="O17" s="50" t="n"/>
+      <c r="P17" s="50" t="n"/>
+      <c r="Q17" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="R17" s="26" t="n"/>
+      <c r="S17" s="26" t="n"/>
+      <c r="T17" s="26" t="n"/>
+      <c r="U17" s="26" t="n"/>
+      <c r="V17" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="W17" s="30" t="n"/>
+      <c r="X17" s="30" t="n"/>
+      <c r="Y17" s="30" t="n"/>
+      <c r="Z17" s="30" t="n"/>
+      <c r="AA17" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB17" s="51" t="n"/>
+      <c r="AC17" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+      <c r="AD17" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE17" s="102" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="C18" s="80" t="inlineStr">
+        <is>
+          <t>教員辦公室</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>T6</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>46218</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N18" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="O18" s="50" t="n"/>
+      <c r="P18" s="50" t="n"/>
+      <c r="Q18" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="R18" s="26" t="n"/>
+      <c r="S18" s="26" t="n"/>
+      <c r="T18" s="26" t="n"/>
+      <c r="U18" s="26" t="n"/>
+      <c r="V18" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="W18" s="30" t="n"/>
+      <c r="X18" s="30" t="n"/>
+      <c r="Y18" s="30" t="n"/>
+      <c r="Z18" s="30" t="n"/>
+      <c r="AA18" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB18" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AC18" s="52" t="n"/>
+      <c r="AD18" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE18" s="102" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="B19" s="10" t="inlineStr">
+        <is>
+          <t>2F</t>
+        </is>
+      </c>
+      <c r="C19" s="80" t="inlineStr">
+        <is>
+          <t>傳道房 + 衛浴</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>T6/T1</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>46218</v>
+      </c>
+      <c r="F19" s="9" t="n">
+        <v>46346</v>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="N19" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="O19" s="103" t="inlineStr">
+        <is>
+          <t>泥作</t>
+        </is>
+      </c>
+      <c r="P19" s="49" t="n"/>
+      <c r="Q19" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="R19" s="26" t="n"/>
+      <c r="S19" s="26" t="n"/>
+      <c r="T19" s="26" t="n"/>
+      <c r="U19" s="26" t="n"/>
+      <c r="V19" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="W19" s="30" t="n"/>
+      <c r="X19" s="30" t="n"/>
+      <c r="Y19" s="30" t="n"/>
+      <c r="Z19" s="30" t="n"/>
+      <c r="AA19" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB19" s="51" t="n"/>
+      <c r="AC19" s="51" t="n"/>
+      <c r="AD19" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AE19" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="C20" s="80" t="inlineStr">
+        <is>
+          <t>音控室</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>T8</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>46225</v>
+      </c>
+      <c r="F20" s="9" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="O20" s="101" t="inlineStr">
+        <is>
+          <t>拆除</t>
+        </is>
+      </c>
+      <c r="P20" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="Q20" s="50" t="n"/>
+      <c r="R20" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="S20" s="26" t="n"/>
+      <c r="T20" s="26" t="n"/>
+      <c r="U20" s="26" t="n"/>
+      <c r="V20" s="26" t="n"/>
+      <c r="W20" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="X20" s="30" t="n"/>
+      <c r="Y20" s="30" t="n"/>
+      <c r="Z20" s="30" t="n"/>
+      <c r="AA20" s="30" t="n"/>
+      <c r="AB20" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AC20" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AD20" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE20" s="102" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="B21" s="10" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="C21" s="80" t="inlineStr">
+        <is>
+          <t>男/女/無障礙廁所 + 儲藏</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>T1</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>46225</v>
+      </c>
+      <c r="F21" s="9" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="O21" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="P21" s="103" t="inlineStr">
+        <is>
+          <t>泥作</t>
+        </is>
+      </c>
+      <c r="Q21" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="R21" s="26" t="n"/>
+      <c r="S21" s="26" t="n"/>
+      <c r="T21" s="26" t="n"/>
+      <c r="U21" s="26" t="n"/>
+      <c r="V21" s="26" t="n"/>
+      <c r="W21" s="26" t="n"/>
+      <c r="X21" s="26" t="n"/>
+      <c r="Y21" s="26" t="n"/>
+      <c r="Z21" s="26" t="n"/>
+      <c r="AA21" s="26" t="n"/>
+      <c r="AB21" s="26" t="n"/>
+      <c r="AC21" s="26" t="n"/>
+      <c r="AD21" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AE21" s="41" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="n">
+        <v>17</v>
+      </c>
+      <c r="B22" s="10" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="C22" s="80" t="inlineStr">
+        <is>
+          <t>副堂</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>T2</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>46230</v>
+      </c>
+      <c r="F22" s="9" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P22" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="Q22" s="50" t="n"/>
+      <c r="R22" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="S22" s="26" t="n"/>
+      <c r="T22" s="26" t="n"/>
+      <c r="U22" s="26" t="n"/>
+      <c r="V22" s="26" t="n"/>
+      <c r="W22" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="X22" s="30" t="n"/>
+      <c r="Y22" s="92" t="inlineStr">
+        <is>
+          <t>石材</t>
+        </is>
+      </c>
+      <c r="Z22" s="32" t="n"/>
+      <c r="AA22" s="32" t="n"/>
+      <c r="AB22" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AC22" s="51" t="n"/>
+      <c r="AD22" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE22" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="C23" s="80" t="inlineStr">
+        <is>
+          <t>交誼廳</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>T3</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>46230</v>
+      </c>
+      <c r="F23" s="9" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P23" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="Q23" s="50" t="n"/>
+      <c r="R23" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="S23" s="26" t="n"/>
+      <c r="T23" s="26" t="n"/>
+      <c r="U23" s="26" t="n"/>
+      <c r="V23" s="26" t="n"/>
+      <c r="W23" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="X23" s="92" t="inlineStr">
+        <is>
+          <t>石材</t>
+        </is>
+      </c>
+      <c r="Y23" s="32" t="n"/>
+      <c r="Z23" s="32" t="n"/>
+      <c r="AA23" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB23" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AC23" s="52" t="n"/>
+      <c r="AD23" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+      <c r="AE23" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="B24" s="10" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="C24" s="80" t="inlineStr">
+        <is>
+          <t>哺乳室</t>
+        </is>
+      </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>T1/T5</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>46230</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P24" s="103" t="inlineStr">
+        <is>
+          <t>泥作</t>
+        </is>
+      </c>
+      <c r="Q24" s="49" t="n"/>
+      <c r="R24" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="S24" s="26" t="n"/>
+      <c r="T24" s="26" t="n"/>
+      <c r="U24" s="26" t="n"/>
+      <c r="V24" s="26" t="n"/>
+      <c r="W24" s="26" t="n"/>
+      <c r="X24" s="26" t="n"/>
+      <c r="Y24" s="26" t="n"/>
+      <c r="Z24" s="26" t="n"/>
+      <c r="AA24" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AB24" s="51" t="n"/>
+      <c r="AC24" s="51" t="n"/>
+      <c r="AD24" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AE24" s="96" t="inlineStr">
+        <is>
+          <t>燈具</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>3F</t>
+        </is>
+      </c>
+      <c r="C25" s="80" t="inlineStr">
+        <is>
+          <t>男寢/女寢/客房/傳道客房</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>T4</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>46230</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <v>46344</v>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="P25" s="89" t="inlineStr">
+        <is>
+          <t>水電</t>
+        </is>
+      </c>
+      <c r="Q25" s="50" t="n"/>
+      <c r="R25" s="90" t="inlineStr">
+        <is>
+          <t>天花</t>
+        </is>
+      </c>
+      <c r="S25" s="26" t="n"/>
+      <c r="T25" s="26" t="n"/>
+      <c r="U25" s="26" t="n"/>
+      <c r="V25" s="26" t="n"/>
+      <c r="W25" s="91" t="inlineStr">
+        <is>
+          <t>木作</t>
+        </is>
+      </c>
+      <c r="X25" s="30" t="n"/>
+      <c r="Y25" s="30" t="n"/>
+      <c r="Z25" s="30" t="n"/>
+      <c r="AA25" s="30" t="n"/>
+      <c r="AB25" s="93" t="inlineStr">
+        <is>
+          <t>油漆</t>
+        </is>
+      </c>
+      <c r="AC25" s="99" t="inlineStr">
+        <is>
+          <t>系統櫃</t>
+        </is>
+      </c>
+      <c r="AD25" s="100" t="inlineStr">
+        <is>
+          <t>設備</t>
+        </is>
+      </c>
+      <c r="AE25" s="97" t="inlineStr">
+        <is>
+          <t>家飾</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" s="47" t="inlineStr">
+        <is>
+          <t>工種圖例</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>鷹架：假設/鷹架</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>拆除：拆除/開孔</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="49" t="n"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>泥作：泥作/防水</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>水電：水電</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>天花：天花(封板)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="30" t="n"/>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>木作：木作</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="32" t="n"/>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>石材：石材</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="35" t="n"/>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>磁磚：磁磚/FMG</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="51" t="n"/>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>油漆：油漆</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>系統櫃：系統櫃/床板</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="20" t="n"/>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>金屬：金屬/床架</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="105" t="n"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>人造石：人造石</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="106" t="n"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>玻璃：玻璃/鏡</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="102" t="n"/>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>燈具：燈具</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="41" t="n"/>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>設備：設備</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="98" t="n"/>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>家飾：家具/窗簾/白板</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" s="53" t="n"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>清潔：清潔</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="M4:P4"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="V4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="AI4"/>
+    <mergeCell ref="Q4:U4"/>
+    <mergeCell ref="AD4:AH4"/>
+    <mergeCell ref="H4:L4"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/工程進度甘特圖.xlsx
+++ b/docs/工程進度甘特圖.xlsx
@@ -12,9 +12,11 @@
     <sheet name="預算總覽" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="工程安排建議" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="分區進場時程" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="採購執行計畫" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'工程進度表'!$A$1:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'採購執行計畫'!$A$4:$H$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -27,7 +29,7 @@
     <numFmt numFmtId="165" formatCode="m/d"/>
     <numFmt numFmtId="166" formatCode="yyyy/m/d"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="24">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -112,8 +114,19 @@
       <color rgb="00FFFFFF"/>
       <sz val="7"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <color rgb="00555555"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="26">
     <fill>
       <patternFill/>
     </fill>
@@ -230,6 +243,16 @@
         <fgColor rgb="00BFA35A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF6E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -265,7 +288,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="125">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -459,6 +482,46 @@
     <xf numFmtId="0" fontId="20" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="25" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6084,4 +6147,1155 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="107" t="inlineStr">
+        <is>
+          <t>碧侯教會 室內裝修工程 — 採購執行計畫（由需求進場日倒推下單/詢價）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="108" t="inlineStr">
+        <is>
+          <t>依詢價啟動日排序；🔴 立即＝啟動日已到(今日 6/15)。下單截止=需求進場−供應期；詢價啟動=下單截止−詢價決標期。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>採購包</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>類別</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>金額(NT$)</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>需求進場</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>下單截止</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>詢價啟動</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>備註</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="109" t="inlineStr">
+        <is>
+          <t>頂樓鋼構(柱/樑/角浪/壁板/強化玻璃門窗)</t>
+        </is>
+      </c>
+      <c r="B5" s="110" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C5" s="111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="112" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E5" s="112" t="n">
+        <v>46178</v>
+      </c>
+      <c r="F5" s="112" t="n">
+        <v>46171</v>
+      </c>
+      <c r="G5" s="113" t="inlineStr">
+        <is>
+          <t>🔴 立即</t>
+        </is>
+      </c>
+      <c r="H5" s="114" t="inlineStr">
+        <is>
+          <t>噴砂+優麗漆；排吊車。已迫切</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="109" t="inlineStr">
+        <is>
+          <t>保護 / 鷹架 分包</t>
+        </is>
+      </c>
+      <c r="B6" s="110" t="inlineStr">
+        <is>
+          <t>連工帶料分包</t>
+        </is>
+      </c>
+      <c r="C6" s="111" t="n">
+        <v>1015700</v>
+      </c>
+      <c r="D6" s="112" t="n">
+        <v>46192</v>
+      </c>
+      <c r="E6" s="112" t="n">
+        <v>46185</v>
+      </c>
+      <c r="F6" s="112" t="n">
+        <v>46178</v>
+      </c>
+      <c r="G6" s="113" t="inlineStr">
+        <is>
+          <t>🔴 立即</t>
+        </is>
+      </c>
+      <c r="H6" s="114" t="inlineStr">
+        <is>
+          <t>已迫切，立即確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="109" t="inlineStr">
+        <is>
+          <t>拆除 分包</t>
+        </is>
+      </c>
+      <c r="B7" s="110" t="inlineStr">
+        <is>
+          <t>連工帶料分包</t>
+        </is>
+      </c>
+      <c r="C7" s="111" t="n">
+        <v>52478</v>
+      </c>
+      <c r="D7" s="112" t="n">
+        <v>46199</v>
+      </c>
+      <c r="E7" s="112" t="n">
+        <v>46192</v>
+      </c>
+      <c r="F7" s="112" t="n">
+        <v>46185</v>
+      </c>
+      <c r="G7" s="113" t="inlineStr">
+        <is>
+          <t>🔴 立即</t>
+        </is>
+      </c>
+      <c r="H7" s="114" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="109" t="inlineStr">
+        <is>
+          <t>水電 分包</t>
+        </is>
+      </c>
+      <c r="B8" s="110" t="inlineStr">
+        <is>
+          <t>連工帶料分包</t>
+        </is>
+      </c>
+      <c r="C8" s="111" t="n">
+        <v>990300</v>
+      </c>
+      <c r="D8" s="112" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E8" s="112" t="n">
+        <v>46199</v>
+      </c>
+      <c r="F8" s="112" t="n">
+        <v>46185</v>
+      </c>
+      <c r="G8" s="113" t="inlineStr">
+        <is>
+          <t>🔴 立即</t>
+        </is>
+      </c>
+      <c r="H8" s="114" t="inlineStr">
+        <is>
+          <t>暫估、待確認項目</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="109" t="inlineStr">
+        <is>
+          <t>泥作防水(界定+發包)</t>
+        </is>
+      </c>
+      <c r="B9" s="110" t="inlineStr">
+        <is>
+          <t>業主自辦/未含</t>
+        </is>
+      </c>
+      <c r="C9" s="111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="112" t="n">
+        <v>46206</v>
+      </c>
+      <c r="E9" s="112" t="n">
+        <v>46199</v>
+      </c>
+      <c r="F9" s="112" t="n">
+        <v>46185</v>
+      </c>
+      <c r="G9" s="113" t="inlineStr">
+        <is>
+          <t>🔴 立即</t>
+        </is>
+      </c>
+      <c r="H9" s="114" t="inlineStr">
+        <is>
+          <t>尚未評估；關鍵路徑</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="115" t="inlineStr">
+        <is>
+          <t>石材(雅典白/小雕刻白 連工帶料)</t>
+        </is>
+      </c>
+      <c r="B10" s="116" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C10" s="117" t="n">
+        <v>1843884</v>
+      </c>
+      <c r="D10" s="118" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E10" s="118" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F10" s="118" t="n">
+        <v>46199</v>
+      </c>
+      <c r="G10" s="119" t="inlineStr">
+        <is>
+          <t>🟡 將到</t>
+        </is>
+      </c>
+      <c r="H10" s="120" t="inlineStr">
+        <is>
+          <t>進口/開料/水磨；先封樣放樣</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="115" t="inlineStr">
+        <is>
+          <t>輕鋼架 分包(含板材)</t>
+        </is>
+      </c>
+      <c r="B11" s="116" t="inlineStr">
+        <is>
+          <t>連工帶料分包</t>
+        </is>
+      </c>
+      <c r="C11" s="117" t="n">
+        <v>1793700</v>
+      </c>
+      <c r="D11" s="118" t="n">
+        <v>46227</v>
+      </c>
+      <c r="E11" s="118" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F11" s="118" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G11" s="119" t="inlineStr">
+        <is>
+          <t>🟡 將到</t>
+        </is>
+      </c>
+      <c r="H11" s="120" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="115" t="inlineStr">
+        <is>
+          <t>空調(界定+發包)</t>
+        </is>
+      </c>
+      <c r="B12" s="116" t="inlineStr">
+        <is>
+          <t>業主自辦/未含</t>
+        </is>
+      </c>
+      <c r="C12" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D12" s="118" t="n">
+        <v>46234</v>
+      </c>
+      <c r="E12" s="118" t="n">
+        <v>46220</v>
+      </c>
+      <c r="F12" s="118" t="n">
+        <v>46206</v>
+      </c>
+      <c r="G12" s="119" t="inlineStr">
+        <is>
+          <t>🟡 將到</t>
+        </is>
+      </c>
+      <c r="H12" s="120" t="inlineStr">
+        <is>
+          <t>未含；封板前需點位</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="115" t="inlineStr">
+        <is>
+          <t>天花板材(大建009S/622N/矽酸鈣/PVC)</t>
+        </is>
+      </c>
+      <c r="B13" s="116" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C13" s="117" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D13" s="118" t="n">
+        <v>46230</v>
+      </c>
+      <c r="E13" s="118" t="n">
+        <v>46216</v>
+      </c>
+      <c r="F13" s="118" t="n">
+        <v>46209</v>
+      </c>
+      <c r="G13" s="119" t="inlineStr">
+        <is>
+          <t>🟡 將到</t>
+        </is>
+      </c>
+      <c r="H13" s="120" t="inlineStr">
+        <is>
+          <t>隨輕鋼架分包</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="58" t="inlineStr">
+        <is>
+          <t>廠製木門 + 門框(實木/鐵杉)</t>
+        </is>
+      </c>
+      <c r="B14" s="121" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C14" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="123" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E14" s="123" t="n">
+        <v>46227</v>
+      </c>
+      <c r="F14" s="123" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G14" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H14" s="124" t="inlineStr">
+        <is>
+          <t>門表確認後製作</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="58" t="inlineStr">
+        <is>
+          <t>木作主材(夾板/白橡木皮/鐵杉/美耐板/吸音格柵)</t>
+        </is>
+      </c>
+      <c r="B15" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C15" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D15" s="123" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E15" s="123" t="n">
+        <v>46227</v>
+      </c>
+      <c r="F15" s="123" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G15" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H15" s="124" t="inlineStr">
+        <is>
+          <t>封樣後下單</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t>木作 分包</t>
+        </is>
+      </c>
+      <c r="B16" s="121" t="inlineStr">
+        <is>
+          <t>連工帶料分包</t>
+        </is>
+      </c>
+      <c r="C16" s="122" t="n">
+        <v>1848590</v>
+      </c>
+      <c r="D16" s="123" t="n">
+        <v>46248</v>
+      </c>
+      <c r="E16" s="123" t="n">
+        <v>46234</v>
+      </c>
+      <c r="F16" s="123" t="n">
+        <v>46220</v>
+      </c>
+      <c r="G16" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H16" s="124" t="inlineStr">
+        <is>
+          <t>含廠製門協調</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="58" t="inlineStr">
+        <is>
+          <t>防墜網(特多龍)</t>
+        </is>
+      </c>
+      <c r="B17" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C17" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D17" s="123" t="n">
+        <v>46244</v>
+      </c>
+      <c r="E17" s="123" t="n">
+        <v>46230</v>
+      </c>
+      <c r="F17" s="123" t="n">
+        <v>46223</v>
+      </c>
+      <c r="G17" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H17" s="124" t="inlineStr">
+        <is>
+          <t>安全考量→高處作業前到場</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="58" t="inlineStr">
+        <is>
+          <t>系統櫃(聖器室/吧台/大廳/辦公)</t>
+        </is>
+      </c>
+      <c r="B18" s="121" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C18" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D18" s="123" t="n">
+        <v>46304</v>
+      </c>
+      <c r="E18" s="123" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F18" s="123" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G18" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H18" s="124" t="inlineStr">
+        <is>
+          <t>板材/五金確認後下單</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="58" t="inlineStr">
+        <is>
+          <t>被褥櫃 56 組 + 床板 62 片</t>
+        </is>
+      </c>
+      <c r="B19" s="121" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C19" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="123" t="n">
+        <v>46311</v>
+      </c>
+      <c r="E19" s="123" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F19" s="123" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G19" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H19" s="124" t="inlineStr">
+        <is>
+          <t>量大、分批進場</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="58" t="inlineStr">
+        <is>
+          <t>地坪(界定+發包)</t>
+        </is>
+      </c>
+      <c r="B20" s="121" t="inlineStr">
+        <is>
+          <t>業主自辦/未含</t>
+        </is>
+      </c>
+      <c r="C20" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D20" s="123" t="n">
+        <v>46269</v>
+      </c>
+      <c r="E20" s="123" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F20" s="123" t="n">
+        <v>46241</v>
+      </c>
+      <c r="G20" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H20" s="124" t="inlineStr">
+        <is>
+          <t>未含；影響石材收頭高程</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="58" t="inlineStr">
+        <is>
+          <t>FMG 大板磚(冰河石)</t>
+        </is>
+      </c>
+      <c r="B21" s="121" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C21" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="123" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E21" s="123" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F21" s="123" t="n">
+        <v>46248</v>
+      </c>
+      <c r="G21" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H21" s="124" t="inlineStr">
+        <is>
+          <t>報價標示取消→須先確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="58" t="inlineStr">
+        <is>
+          <t>金屬床架(13雙/5單+護欄+爬梯)</t>
+        </is>
+      </c>
+      <c r="B22" s="121" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C22" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="123" t="n">
+        <v>46321</v>
+      </c>
+      <c r="E22" s="123" t="n">
+        <v>46279</v>
+      </c>
+      <c r="F22" s="123" t="n">
+        <v>46272</v>
+      </c>
+      <c r="G22" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H22" s="124" t="inlineStr">
+        <is>
+          <t>金屬工程</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t>立式烘碗機 VVR-180 ×2</t>
+        </is>
+      </c>
+      <c r="B23" s="121" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C23" s="122" t="n">
+        <v>130000</v>
+      </c>
+      <c r="D23" s="123" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E23" s="123" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F23" s="123" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G23" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H23" s="124" t="inlineStr">
+        <is>
+          <t>可能訂製</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="58" t="inlineStr">
+        <is>
+          <t>磁磚貼工 分包</t>
+        </is>
+      </c>
+      <c r="B24" s="121" t="inlineStr">
+        <is>
+          <t>連工帶料分包</t>
+        </is>
+      </c>
+      <c r="C24" s="122" t="n">
+        <v>135660</v>
+      </c>
+      <c r="D24" s="123" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E24" s="123" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F24" s="123" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G24" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H24" s="124" t="inlineStr">
+        <is>
+          <t>僅貼工</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="58" t="inlineStr">
+        <is>
+          <t>油漆(界定+發包)</t>
+        </is>
+      </c>
+      <c r="B25" s="121" t="inlineStr">
+        <is>
+          <t>業主自辦/未含</t>
+        </is>
+      </c>
+      <c r="C25" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D25" s="123" t="n">
+        <v>46290</v>
+      </c>
+      <c r="E25" s="123" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F25" s="123" t="n">
+        <v>46276</v>
+      </c>
+      <c r="G25" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H25" s="124" t="inlineStr">
+        <is>
+          <t>未含；木作後/燈具前</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="58" t="inlineStr">
+        <is>
+          <t>多媒體白板 W411 ×4 + 白板</t>
+        </is>
+      </c>
+      <c r="B26" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C26" s="122" t="n">
+        <v>150360</v>
+      </c>
+      <c r="D26" s="123" t="n">
+        <v>46321</v>
+      </c>
+      <c r="E26" s="123" t="n">
+        <v>46293</v>
+      </c>
+      <c r="F26" s="123" t="n">
+        <v>46286</v>
+      </c>
+      <c r="G26" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H26" s="124" t="inlineStr">
+        <is>
+          <t>不含電視</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="58" t="inlineStr">
+        <is>
+          <t>機櫃 19" ×2</t>
+        </is>
+      </c>
+      <c r="B27" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C27" s="122" t="n">
+        <v>46400</v>
+      </c>
+      <c r="D27" s="123" t="n">
+        <v>46323</v>
+      </c>
+      <c r="E27" s="123" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F27" s="123" t="n">
+        <v>46288</v>
+      </c>
+      <c r="G27" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H27" s="124" t="inlineStr">
+        <is>
+          <t>訂製</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="58" t="inlineStr">
+        <is>
+          <t>照明燈具(崁燈/平板/大量;含停產替代)</t>
+        </is>
+      </c>
+      <c r="B28" s="121" t="inlineStr">
+        <is>
+          <t>關鍵長交期(A)</t>
+        </is>
+      </c>
+      <c r="C28" s="122" t="n">
+        <v>433384</v>
+      </c>
+      <c r="D28" s="123" t="n">
+        <v>46328</v>
+      </c>
+      <c r="E28" s="123" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F28" s="123" t="n">
+        <v>46293</v>
+      </c>
+      <c r="G28" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H28" s="124" t="inlineStr">
+        <is>
+          <t>T5停產/型號需替代→提早確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="58" t="inlineStr">
+        <is>
+          <t>人造石檯面(樂天PC842)</t>
+        </is>
+      </c>
+      <c r="B29" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C29" s="122" t="n">
+        <v>207088</v>
+      </c>
+      <c r="D29" s="123" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E29" s="123" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F29" s="123" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G29" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H29" s="124" t="inlineStr">
+        <is>
+          <t>櫃體丈量後製作</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="58" t="inlineStr">
+        <is>
+          <t>玻璃 / 鏡(烤漆/清/明鏡/灰鏡)</t>
+        </is>
+      </c>
+      <c r="B30" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C30" s="122" t="n">
+        <v>57491</v>
+      </c>
+      <c r="D30" s="123" t="n">
+        <v>46318</v>
+      </c>
+      <c r="E30" s="123" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F30" s="123" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G30" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H30" s="124" t="inlineStr">
+        <is>
+          <t>現場丈量後</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="58" t="inlineStr">
+        <is>
+          <t>設備(飲水機/冰箱/水槽/龍頭/各式扇/殺菌機)</t>
+        </is>
+      </c>
+      <c r="B31" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C31" s="122" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="123" t="n">
+        <v>46325</v>
+      </c>
+      <c r="E31" s="123" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F31" s="123" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G31" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H31" s="124" t="inlineStr">
+        <is>
+          <t>設備工程一式</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="58" t="inlineStr">
+        <is>
+          <t>防火捲簾 + 鋁百葉(大量)</t>
+        </is>
+      </c>
+      <c r="B32" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C32" s="122" t="n">
+        <v>377280</v>
+      </c>
+      <c r="D32" s="123" t="n">
+        <v>46332</v>
+      </c>
+      <c r="E32" s="123" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F32" s="123" t="n">
+        <v>46297</v>
+      </c>
+      <c r="G32" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H32" s="124" t="inlineStr">
+        <is>
+          <t>防火認證文件；丈量後製作</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="58" t="inlineStr">
+        <is>
+          <t>消防設備(探測器/廣播/緊急照明 延伸)</t>
+        </is>
+      </c>
+      <c r="B33" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C33" s="122" t="n">
+        <v>225132</v>
+      </c>
+      <c r="D33" s="123" t="n">
+        <v>46328</v>
+      </c>
+      <c r="E33" s="123" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F33" s="123" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G33" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H33" s="124" t="inlineStr">
+        <is>
+          <t>與既有整合</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="58" t="inlineStr">
+        <is>
+          <t>銘版(不鏽鋼字/貼紙)</t>
+        </is>
+      </c>
+      <c r="B34" s="121" t="inlineStr">
+        <is>
+          <t>一般材料(B)</t>
+        </is>
+      </c>
+      <c r="C34" s="122" t="n">
+        <v>41120</v>
+      </c>
+      <c r="D34" s="123" t="n">
+        <v>46335</v>
+      </c>
+      <c r="E34" s="123" t="n">
+        <v>46314</v>
+      </c>
+      <c r="F34" s="123" t="n">
+        <v>46307</v>
+      </c>
+      <c r="G34" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H34" s="124" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="58" t="inlineStr">
+        <is>
+          <t>環境清潔 分包</t>
+        </is>
+      </c>
+      <c r="B35" s="121" t="inlineStr">
+        <is>
+          <t>連工帶料分包</t>
+        </is>
+      </c>
+      <c r="C35" s="122" t="n">
+        <v>352500</v>
+      </c>
+      <c r="D35" s="123" t="n">
+        <v>46339</v>
+      </c>
+      <c r="E35" s="123" t="n">
+        <v>46332</v>
+      </c>
+      <c r="F35" s="123" t="n">
+        <v>46325</v>
+      </c>
+      <c r="G35" s="54" t="inlineStr">
+        <is>
+          <t>待辦</t>
+        </is>
+      </c>
+      <c r="H35" s="124" t="inlineStr">
+        <is>
+          <t>粗清+細清</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:H35"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>